--- a/swap_implied_input/input_master_6m.xlsx
+++ b/swap_implied_input/input_master_6m.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -514,6 +514,326 @@
         <v>-152.96</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-02-09</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>3.57871</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1.2725</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-152.97</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-02-10</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>3.57871</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1.2668</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-152.18</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-02-11</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>3.58072</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1.2653</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-151.3</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-02-12</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>3.56016</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1.2621</v>
+      </c>
+      <c r="D9" t="n">
+        <v>-153.3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-02-13</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>3.56016</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.2621</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-153</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>3.60068</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1.2621</v>
+      </c>
+      <c r="D11" t="n">
+        <v>-154.37</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-02-16</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>3.60068</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1.263</v>
+      </c>
+      <c r="D12" t="n">
+        <v>-152.76</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-02-19</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>3.59442</v>
+      </c>
+      <c r="C13" t="n">
+        <v>1.266</v>
+      </c>
+      <c r="D13" t="n">
+        <v>-154.5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-02-20</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>3.59442</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1.2686</v>
+      </c>
+      <c r="D14" t="n">
+        <v>-153.48</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>3.6077</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1.2663</v>
+      </c>
+      <c r="D15" t="n">
+        <v>-154.25</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-02-25</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>3.61885</v>
+      </c>
+      <c r="C16" t="n">
+        <v>1.267</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-154.9</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-02-26</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>3.62527</v>
+      </c>
+      <c r="C17" t="n">
+        <v>1.2641</v>
+      </c>
+      <c r="D17" t="n">
+        <v>-155.75</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>3.62607</v>
+      </c>
+      <c r="C18" t="n">
+        <v>1.2638</v>
+      </c>
+      <c r="D18" t="n">
+        <v>-156.5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>3.64135</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1.282</v>
+      </c>
+      <c r="D19" t="n">
+        <v>-161.4</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>3.61733</v>
+      </c>
+      <c r="C20" t="n">
+        <v>1.273</v>
+      </c>
+      <c r="D20" t="n">
+        <v>-159.74</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>3.63819</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1.273</v>
+      </c>
+      <c r="D21" t="n">
+        <v>-162.5</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>3.62809</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1.2775</v>
+      </c>
+      <c r="D22" t="n">
+        <v>-164.01</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-03-16</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>3.66403</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1.2829</v>
+      </c>
+      <c r="D23" t="n">
+        <v>-163</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>3.66403</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1.2829</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-162.41</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>3.66816</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1.2769</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-163.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/swap_implied_input/input_master_6m.xlsx
+++ b/swap_implied_input/input_master_6m.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -834,6 +834,70 @@
         <v>-163.5</v>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>3.66758</v>
+      </c>
+      <c r="C26" t="n">
+        <v>1.2814</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-162.895</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>3.66791</v>
+      </c>
+      <c r="C27" t="n">
+        <v>1.2796</v>
+      </c>
+      <c r="D27" t="n">
+        <v>-162.98</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>3.67764</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1.2816</v>
+      </c>
+      <c r="D28" t="n">
+        <v>-165.02</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>3.72813</v>
+      </c>
+      <c r="C29" t="n">
+        <v>1.2751</v>
+      </c>
+      <c r="D29" t="n">
+        <v>-164.25</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
